--- a/templates/[웨이즈원]기초번호판설치점검_주간보고_템플릿.xlsx
+++ b/templates/[웨이즈원]기초번호판설치점검_주간보고_템플릿.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PSM\Downloads\public-보고서\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C986C937-32DF-44AA-8745-F8937BE5899E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7707A99C-D9A1-4896-B057-E6CD1BD7656E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -255,6 +255,12 @@
     <t>□ 금주 실적</t>
   </si>
   <si>
+    <t>□ 추진계획</t>
+  </si>
+  <si>
+    <t>□ 기타</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -291,699 +297,544 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t>금주 추진 내용을 자유롭게 작성하세요</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF595959"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">.
+      <t>특이사항 등</t>
+    </r>
+  </si>
+  <si>
+    <t>지역별 주간 점검 실적 입력</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF9C5700"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>▶ '</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF9C5700"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>금주점검건수</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF9C5700"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">' </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF9C5700"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">칸만 입력하세요 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF9C5700"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF9C5700"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">착수 초기에는 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF9C5700"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">0 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF9C5700"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>그대로 저장해도 됩니다</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF9C5700"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>※ 정상</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>훼손</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">망실은 </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">KAIS </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>설치현황 파일 업로드 시 자동 집계됩니다</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>여기서는 입력 불필요</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF7F7F7F"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>시도</t>
+  </si>
+  <si>
+    <t>시군구</t>
+  </si>
+  <si>
+    <t>전체대상건수</t>
+  </si>
+  <si>
+    <t>금주점검건수</t>
+  </si>
+  <si>
+    <t>강원특별자치도</t>
+  </si>
+  <si>
+    <t>고성군</t>
+  </si>
+  <si>
+    <t>양구군</t>
+  </si>
+  <si>
+    <t>양양군</t>
+  </si>
+  <si>
+    <t>춘천시</t>
+  </si>
+  <si>
+    <t>홍천군</t>
+  </si>
+  <si>
+    <t>경기도</t>
+  </si>
+  <si>
+    <t>동두천시</t>
+  </si>
+  <si>
+    <t>여주시</t>
+  </si>
+  <si>
+    <t>충청남도</t>
+  </si>
+  <si>
+    <t>금산군</t>
+  </si>
+  <si>
+    <t>충청북도</t>
+  </si>
+  <si>
+    <t>제천시</t>
+  </si>
+  <si>
+    <t>청주시 상당구</t>
+  </si>
+  <si>
+    <t>청주시 서원구</t>
+  </si>
+  <si>
+    <t>청주시 청원구</t>
+  </si>
+  <si>
+    <t>합 계</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>※ 파일명 형식</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>: [</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>웨이즈원</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>]</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>기초번호판설치점검</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>주간보고</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>_YYYYMMDD.xlsx  (</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>날짜</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>매주 목요일</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>[입력] 금주</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>추진</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>내용을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>자유롭게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">작성하세요.
 </t>
     </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF595959"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>예</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF595959"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">)
-- </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF595959"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">착수보고회 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF595959"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>(7</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF595959"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">월 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF595959"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>9</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF595959"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>일</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF595959"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">)
-- </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF595959"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>스마트</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF595959"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">KAIS </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF595959"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">사용자 계정 요청
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[입력] 차주</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>계획을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">작성하세요.
 </t>
     </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF595959"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">- </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF595959"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>지자체별 점검수량 파악</t>
-    </r>
-  </si>
-  <si>
-    <t>□ 추진계획</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF595959"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF595959"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>입력</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF595959"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">] </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF595959"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>차주 계획을 작성하세요</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF595959"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF595959"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>예</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF595959"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">)
-- </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF595959"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">현장조사팀 배정
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF595959"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">- </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF595959"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>현장 점검 시작</t>
-    </r>
-  </si>
-  <si>
-    <t>□ 기타</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF595959"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF595959"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>입력</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF595959"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">] </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF595959"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>특이사항 등</t>
-    </r>
-  </si>
-  <si>
-    <t>지역별 주간 점검 실적 입력</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FF9C5700"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>▶ '</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FF9C5700"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>금주점검건수</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FF9C5700"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">' </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FF9C5700"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">칸만 입력하세요 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FF9C5700"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FF9C5700"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">착수 초기에는 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FF9C5700"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">0 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FF9C5700"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>그대로 저장해도 됩니다</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FF9C5700"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>※ 정상</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>훼손</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">망실은 </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">KAIS </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>설치현황 파일 업로드 시 자동 집계됩니다</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>여기서는 입력 불필요</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>시도</t>
-  </si>
-  <si>
-    <t>시군구</t>
-  </si>
-  <si>
-    <t>전체대상건수</t>
-  </si>
-  <si>
-    <t>금주점검건수</t>
-  </si>
-  <si>
-    <t>강원특별자치도</t>
-  </si>
-  <si>
-    <t>고성군</t>
-  </si>
-  <si>
-    <t>양구군</t>
-  </si>
-  <si>
-    <t>양양군</t>
-  </si>
-  <si>
-    <t>춘천시</t>
-  </si>
-  <si>
-    <t>홍천군</t>
-  </si>
-  <si>
-    <t>경기도</t>
-  </si>
-  <si>
-    <t>동두천시</t>
-  </si>
-  <si>
-    <t>여주시</t>
-  </si>
-  <si>
-    <t>충청남도</t>
-  </si>
-  <si>
-    <t>금산군</t>
-  </si>
-  <si>
-    <t>충청북도</t>
-  </si>
-  <si>
-    <t>제천시</t>
-  </si>
-  <si>
-    <t>청주시 상당구</t>
-  </si>
-  <si>
-    <t>청주시 서원구</t>
-  </si>
-  <si>
-    <t>청주시 청원구</t>
-  </si>
-  <si>
-    <t>합 계</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>※ 파일명 형식</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>: [</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>웨이즈원</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>]</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>기초번호판설치점검</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>_</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>주간보고</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>_YYYYMMDD.xlsx  (</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>날짜</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>=</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>매주 목요일</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>)</t>
-    </r>
+    <phoneticPr fontId="20" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1130,6 +981,12 @@
       <name val="돋움"/>
       <family val="3"/>
       <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF595959"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="8">
@@ -1262,24 +1119,21 @@
     <xf numFmtId="3" fontId="17" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1293,6 +1147,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1565,214 +1422,209 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="27.75" customHeight="1">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
     </row>
     <row r="4" spans="1:6" ht="15" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
     </row>
     <row r="5" spans="1:6" ht="15" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="17"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
     </row>
     <row r="6" spans="1:6" ht="15" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
     </row>
     <row r="8" spans="1:6" ht="18" customHeight="1">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
+      <c r="B8" s="15"/>
+      <c r="C8" s="15"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="15"/>
     </row>
     <row r="9" spans="1:6" ht="79.5" customHeight="1">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" s="22"/>
+      <c r="C9" s="22"/>
+      <c r="D9" s="22"/>
+      <c r="E9" s="22"/>
+      <c r="F9" s="22"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="22"/>
+      <c r="B10" s="22"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="22"/>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="22"/>
+      <c r="B11" s="22"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="22"/>
+      <c r="E11" s="22"/>
+      <c r="F11" s="22"/>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="22"/>
+      <c r="B12" s="22"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="22"/>
+      <c r="E12" s="22"/>
+      <c r="F12" s="22"/>
+    </row>
+    <row r="14" spans="1:6" ht="18" customHeight="1">
+      <c r="A14" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="13"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="13"/>
-      <c r="B10" s="13"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="13"/>
-      <c r="B11" s="13"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="13"/>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-    </row>
-    <row r="14" spans="1:6" ht="18" customHeight="1">
-      <c r="A14" s="12" t="s">
+      <c r="B14" s="15"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
+    </row>
+    <row r="15" spans="1:6" ht="79.5" customHeight="1">
+      <c r="A15" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="22"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="22"/>
+      <c r="E15" s="22"/>
+      <c r="F15" s="22"/>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="22"/>
+      <c r="B16" s="22"/>
+      <c r="C16" s="22"/>
+      <c r="D16" s="22"/>
+      <c r="E16" s="22"/>
+      <c r="F16" s="22"/>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="22"/>
+      <c r="B17" s="22"/>
+      <c r="C17" s="22"/>
+      <c r="D17" s="22"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="22"/>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="22"/>
+      <c r="B18" s="22"/>
+      <c r="C18" s="22"/>
+      <c r="D18" s="22"/>
+      <c r="E18" s="22"/>
+      <c r="F18" s="22"/>
+    </row>
+    <row r="20" spans="1:6" ht="18" customHeight="1">
+      <c r="A20" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="12"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
-    </row>
-    <row r="15" spans="1:6" ht="79.5" customHeight="1">
-      <c r="A15" s="13" t="s">
+      <c r="B20" s="15"/>
+      <c r="C20" s="15"/>
+      <c r="D20" s="15"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="15"/>
+    </row>
+    <row r="21" spans="1:6" ht="79.5" customHeight="1">
+      <c r="A21" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="13"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="13"/>
-      <c r="B16" s="13"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="13"/>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="13"/>
-      <c r="B17" s="13"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="13"/>
-      <c r="B18" s="13"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
-    </row>
-    <row r="20" spans="1:6" ht="18" customHeight="1">
-      <c r="A20" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B20" s="12"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
-    </row>
-    <row r="21" spans="1:6" ht="79.5" customHeight="1">
-      <c r="A21" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="B21" s="13"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
+      <c r="B21" s="22"/>
+      <c r="C21" s="22"/>
+      <c r="D21" s="22"/>
+      <c r="E21" s="22"/>
+      <c r="F21" s="22"/>
     </row>
     <row r="22" spans="1:6">
-      <c r="A22" s="13"/>
-      <c r="B22" s="13"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13"/>
+      <c r="A22" s="22"/>
+      <c r="B22" s="22"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="22"/>
     </row>
     <row r="23" spans="1:6">
-      <c r="A23" s="13"/>
-      <c r="B23" s="13"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
+      <c r="A23" s="22"/>
+      <c r="B23" s="22"/>
+      <c r="C23" s="22"/>
+      <c r="D23" s="22"/>
+      <c r="E23" s="22"/>
+      <c r="F23" s="22"/>
     </row>
     <row r="24" spans="1:6">
-      <c r="A24" s="13"/>
-      <c r="B24" s="13"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
+      <c r="A24" s="22"/>
+      <c r="B24" s="22"/>
+      <c r="C24" s="22"/>
+      <c r="D24" s="22"/>
+      <c r="E24" s="22"/>
+      <c r="F24" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="B5:F5"/>
     <mergeCell ref="A20:F20"/>
     <mergeCell ref="A21:F24"/>
     <mergeCell ref="B6:F6"/>
@@ -1780,6 +1632,11 @@
     <mergeCell ref="A9:F12"/>
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="A15:F18"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="B5:F5"/>
   </mergeCells>
   <phoneticPr fontId="20" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1799,47 +1656,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="25.5" customHeight="1">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+    </row>
+    <row r="2" spans="1:5" ht="15" customHeight="1">
+      <c r="A2" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+    </row>
+    <row r="3" spans="1:5" ht="15" customHeight="1">
+      <c r="A3" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-    </row>
-    <row r="2" spans="1:5" ht="15" customHeight="1">
-      <c r="A2" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-    </row>
-    <row r="3" spans="1:5" ht="15" customHeight="1">
-      <c r="A3" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" s="20"/>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
     </row>
     <row r="4" spans="1:5" ht="27.75" customHeight="1">
       <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>22</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1847,10 +1704,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D5" s="6">
         <v>1995</v>
@@ -1864,10 +1721,10 @@
         <v>2</v>
       </c>
       <c r="B6" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="9" t="s">
         <v>25</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>27</v>
       </c>
       <c r="D6" s="10">
         <v>574</v>
@@ -1881,10 +1738,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D7" s="6">
         <v>244</v>
@@ -1898,10 +1755,10 @@
         <v>4</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D8" s="10">
         <v>1611</v>
@@ -1915,10 +1772,10 @@
         <v>5</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D9" s="6">
         <v>1839</v>
@@ -1932,10 +1789,10 @@
         <v>6</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D10" s="10">
         <v>461</v>
@@ -1949,10 +1806,10 @@
         <v>7</v>
       </c>
       <c r="B11" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="5" t="s">
         <v>31</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>33</v>
       </c>
       <c r="D11" s="6">
         <v>993</v>
@@ -1966,10 +1823,10 @@
         <v>8</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D12" s="10">
         <v>1462</v>
@@ -1983,10 +1840,10 @@
         <v>9</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D13" s="6">
         <v>1456</v>
@@ -2000,10 +1857,10 @@
         <v>10</v>
       </c>
       <c r="B14" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" s="9" t="s">
         <v>36</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>38</v>
       </c>
       <c r="D14" s="10">
         <v>552</v>
@@ -2017,10 +1874,10 @@
         <v>11</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D15" s="6">
         <v>79</v>
@@ -2034,10 +1891,10 @@
         <v>12</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D16" s="10">
         <v>610</v>
@@ -2047,11 +1904,11 @@
       </c>
     </row>
     <row r="17" spans="1:5" ht="15" customHeight="1">
-      <c r="A17" s="21" t="s">
-        <v>41</v>
-      </c>
-      <c r="B17" s="21"/>
-      <c r="C17" s="21"/>
+      <c r="A17" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" s="20"/>
+      <c r="C17" s="20"/>
       <c r="D17" s="11">
         <f>SUM(D5:D16)</f>
         <v>11876</v>
@@ -2062,13 +1919,13 @@
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="22" t="s">
-        <v>42</v>
-      </c>
-      <c r="B19" s="22"/>
-      <c r="C19" s="22"/>
-      <c r="D19" s="22"/>
-      <c r="E19" s="22"/>
+      <c r="A19" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="21"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/templates/[웨이즈원]기초번호판설치점검_주간보고_템플릿.xlsx
+++ b/templates/[웨이즈원]기초번호판설치점검_주간보고_템플릿.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PSM\Downloads\public-보고서\깃의 템플릿\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\JavaScript DEV\public-보고서\서버에 업로드_20260819_현재\addr.chk.2026-main\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9CFCC33-7987-4075-A11E-1DFCBDF09C1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="주간보고내용" sheetId="1" r:id="rId1"/>

--- a/templates/[웨이즈원]기초번호판설치점검_주간보고_템플릿.xlsx
+++ b/templates/[웨이즈원]기초번호판설치점검_주간보고_템플릿.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\JavaScript DEV\public-보고서\서버에 업로드_20260819_현재\addr.chk.2026-main\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9CFCC33-7987-4075-A11E-1DFCBDF09C1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3E56A61-0DB7-475B-9F8B-E6AD73D736D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="주간보고내용" sheetId="1" r:id="rId1"/>
     <sheet name="주간실적입력" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -144,12 +144,6 @@
     <t>[입력] 성명</t>
   </si>
   <si>
-    <t>[입력] 예: 2026-07-10 (매주 목요일)</t>
-  </si>
-  <si>
-    <t>[입력] 예: 2026-07-04 ~ 2026-07-10</t>
-  </si>
-  <si>
     <t xml:space="preserve">[입력] 금주 추진 내용을 자유롭게 작성하세요.
 </t>
     <phoneticPr fontId="9" type="noConversion"/>
@@ -170,6 +164,14 @@
   </si>
   <si>
     <t>※ 파일명 형식: [웨이즈원]기초번호판설치점검_주간보고_YYYYMMDD.xlsx  (날짜=매주 목요일)</t>
+  </si>
+  <si>
+    <t>[입력] 예: 2026-08-20 (매주 목요일 기준으로 날짜 작성)</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>[입력] 예: 2026-08-14 ~ 2026-08-20</t>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -403,20 +405,20 @@
     <xf numFmtId="3" fontId="10" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -704,209 +706,214 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
     </row>
     <row r="4" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="C4" s="14"/>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14"/>
+      <c r="B4" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
     </row>
     <row r="5" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="C5" s="14"/>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="14"/>
+      <c r="B5" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
     </row>
     <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
     </row>
     <row r="8" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="15" t="s">
+      <c r="A8" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="15"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15"/>
+      <c r="B8" s="12"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
     </row>
     <row r="9" spans="1:6" ht="79.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="16" t="s">
+      <c r="A9" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="13"/>
+      <c r="C9" s="13"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="13"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="13"/>
+      <c r="B10" s="13"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="13"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="13"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
+    </row>
+    <row r="14" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" s="12"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
+    </row>
+    <row r="15" spans="1:6" ht="79.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="13"/>
+      <c r="B16" s="13"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="13"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="13"/>
+      <c r="B17" s="13"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="13"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="13"/>
+      <c r="B18" s="13"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
+    </row>
+    <row r="20" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="12"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+    </row>
+    <row r="21" spans="1:6" ht="79.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="16"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="16"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="16"/>
-      <c r="B10" s="16"/>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="16"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="16"/>
-      <c r="B11" s="16"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="16"/>
-      <c r="B12" s="16"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-    </row>
-    <row r="14" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="B14" s="15"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
-    </row>
-    <row r="15" spans="1:6" ht="79.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="B15" s="16"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="16"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="16"/>
-      <c r="B16" s="16"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="16"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="16"/>
-      <c r="B17" s="16"/>
-      <c r="C17" s="16"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="16"/>
-      <c r="F17" s="16"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="16"/>
-      <c r="B18" s="16"/>
-      <c r="C18" s="16"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="16"/>
-      <c r="F18" s="16"/>
-    </row>
-    <row r="20" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="B20" s="15"/>
-      <c r="C20" s="15"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15"/>
-    </row>
-    <row r="21" spans="1:6" ht="79.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="B21" s="16"/>
-      <c r="C21" s="16"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="16"/>
-      <c r="F21" s="16"/>
+      <c r="B21" s="13"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="16"/>
-      <c r="B22" s="16"/>
-      <c r="C22" s="16"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="16"/>
+      <c r="A22" s="13"/>
+      <c r="B22" s="13"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="16"/>
-      <c r="B23" s="16"/>
-      <c r="C23" s="16"/>
-      <c r="D23" s="16"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="16"/>
+      <c r="A23" s="13"/>
+      <c r="B23" s="13"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="16"/>
-      <c r="B24" s="16"/>
-      <c r="C24" s="16"/>
-      <c r="D24" s="16"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="16"/>
+      <c r="A24" s="13"/>
+      <c r="B24" s="13"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="B5:F5"/>
     <mergeCell ref="A20:F20"/>
     <mergeCell ref="A21:F24"/>
     <mergeCell ref="B6:F6"/>
@@ -914,11 +921,6 @@
     <mergeCell ref="A9:F12"/>
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="A15:F18"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="B5:F5"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -949,7 +951,7 @@
     </row>
     <row r="2" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="18" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B2" s="18"/>
       <c r="C2" s="18"/>
@@ -958,7 +960,7 @@
     </row>
     <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="19" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B3" s="19"/>
       <c r="C3" s="19"/>
@@ -1203,7 +1205,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="21" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B19" s="21"/>
       <c r="C19" s="21"/>
